--- a/dataset/02.wo_Defects/double_lock.xlsx
+++ b/dataset/02.wo_Defects/double_lock.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pthread_mutex_t double_lock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int double_lock_001_glb_data = 0; pthread_mutex_t double_lock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int double_lock_002_glb_data = 0; pthread_mutex_t double_lock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int double_lock_003_glb_data = 0; pthread_mutex_t double_lock_004_glb_mutex1 = PTHREAD_MUTEX_INITIALIZER; extern volatile int vflag; void double_lock_004 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; long int t1 = 10; long int t2 = 20; sink += pthread_create(&amp;th1, NULL, Thread3, (void *)t1); sink += pthread_create(&amp;th2, NULL, Thread4, (void *)t2); #endif /* defined(CHECKER_POLYSPACE) */ } void *Thread3(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; pthread_mutex_lock( &amp;double_lock_004_glb_mutex1 ); ip = (long)input; ip = ip *10; printf("Task3! It's me, thread #%lu!\n",ip); pthread_mutex_unlock( &amp;double_lock_004_glb_mutex1 ); #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void *Thread4(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; pthread_mutex_lock( &amp;double_lock_004_glb_mutex1 ); /*Tool should not detect this line as error*/ /*No ERROR:Double Lock*/ ip = (long)input; ip = ip *10; printf("Task4! It's me, thread #%lu!\n",ip); pthread_mutex_unlock( &amp;double_lock_004_glb_mutex1 ); #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
+          <t>pthread_mutex_t double_lock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int double_lock_001_glb_data = 0; pthread_mutex_t double_lock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int double_lock_002_glb_data = 0; pthread_mutex_t double_lock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int double_lock_003_glb_data = 0; pthread_mutex_t double_lock_004_glb_mutex1 = PTHREAD_MUTEX_INITIALIZER; extern volatile int vflag; void double_lock_004 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; long int t1 = 10; long int t2 = 20; sink += pthread_create(&amp;th1, NULL, Thread3, (void *)t1); sink += pthread_create(&amp;th2, NULL, Thread4, (void *)t2); #endif /* defined(CHECKER_POLYSPACE) */ } void *Thread4(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; pthread_mutex_lock( &amp;double_lock_004_glb_mutex1 ); /*Tool should not detect this line as error*/ /*No ERROR:Double Lock*/ ip = (long)input; ip = ip *10; printf("Task4! It's me, thread #%lu!\n",ip); pthread_mutex_unlock( &amp;double_lock_004_glb_mutex1 ); #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void *Thread3(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; pthread_mutex_lock( &amp;double_lock_004_glb_mutex1 ); ip = (long)input; ip = ip *10; printf("Task3! It's me, thread #%lu!\n",ip); pthread_mutex_unlock( &amp;double_lock_004_glb_mutex1 ); #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
